--- a/CLASS_ABILITIES.xlsx
+++ b/CLASS_ABILITIES.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="R5920734ec8894147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R15c9d9eee8ae4ef8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="R9f8372037e18495b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="R0ad989e67db14c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="Re621c26b4d7a49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R31368b2449b14af4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="Rb35261cbef854351"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="Re3cb7566bf5248f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -567,7 +567,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3d11dc90ee946fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R914301fd4b7b4699"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -764,7 +764,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bd255d0efe6422c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f9643b0c6c4458e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -878,16 +878,16 @@
         <x:v>Warrior</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
-        <x:v>Charge</x:v>
+        <x:v>Battle Stomp</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>Melee ability. Melee. Range 5.00. Physical damage (weapon damage + Strength x100%). Charges in a clear straight line and stops adjacent. Affects: enemies. Melee weapon required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="57" customHeight="1">
+        <x:v>Melee ability. Cast. Range 1.50. Physical damage (weapon damage + Strength x100%). Radius 1.50 around caster; click caster to confirm. Affects: enemies. Melee weapon required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -898,13 +898,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="23" t="str">
-        <x:v>Bloodlust</x:v>
+        <x:v>Charge</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
-        <x:v>Melee ability. Melee. Range 1.41. Physical damage (weapon damage + Strength x100%), On kill: caster gains Strength Up ×2 (Strength Up: +1 Strength per stack. Until battle ends. Positive status). Affects: enemies. Melee weapon required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+        <x:v>Melee ability. Melee. Range 5.00. Physical damage (weapon damage + Strength x100%). Charges in a clear straight line and stops adjacent. Affects: enemies. Melee weapon required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="57" customHeight="1">
       <x:c r="A10" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -912,13 +912,13 @@
         <x:v>Warrior</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>Battle Stomp</x:v>
+        <x:v>Bloodlust</x:v>
       </x:c>
       <x:c r="E10" s="19" t="str">
-        <x:v>Melee ability. Cast. Range 1.50. Physical damage (weapon damage + Strength x100%). Radius 1.50 around caster; click caster to confirm. Affects: enemies. Melee weapon required.</x:v>
+        <x:v>Melee ability. Melee. Range 1.41. Physical damage (weapon damage + Strength x100%), On kill: caster gains Strength Up ×2 (Strength Up: +1 Strength per stack. Until battle ends. Positive status). Affects: enemies. Melee weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="57" customHeight="1">
@@ -1012,7 +1012,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc3614299014f96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde17544857ef4880"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1209,7 +1209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra002b15ebf594dde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a06072b50794f73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/CLASS_ABILITIES.xlsx
+++ b/CLASS_ABILITIES.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="Re621c26b4d7a49dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R31368b2449b14af4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="Rb35261cbef854351"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="Re3cb7566bf5248f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="R1ab8ac45c29b4288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R88a8eb222de94449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="Rc6e88f29e3464958"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="Rd58e949af40e4fc6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -510,7 +510,7 @@
         <x:v>Ranged ability. Projectile. Range 5.00. Physical damage (weapon damage + Dexterity x60%). Affects: enemies. Can aim at a cell. Ranged weapon required.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="42" customHeight="1">
+    <x:row r="8" ht="57" customHeight="1">
       <x:c r="A8" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -518,16 +518,16 @@
         <x:v>Archer</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
-        <x:v>Focus</x:v>
+        <x:v>Multiple Arrows</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>Magic ability. Cast. Range 0.00. Focus for 2 turns. +2 Strength, +2 Dexterity, +2 Intelligence. Positive status. Affects: self. No weapon required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="57" customHeight="1">
+        <x:v>Ranged ability. Projectile. Range 5.00. Physical damage (3 hits × (weapon damage + Dexterity x60%)). Choose 3 targets in order; repeats allowed; confirm to fire. Affects: enemies. Ranged weapon required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -535,13 +535,13 @@
         <x:v>Archer</x:v>
       </x:c>
       <x:c r="C9" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="23" t="str">
-        <x:v>Multiple Arrows</x:v>
+        <x:v>Focus</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
-        <x:v>Ranged ability. Projectile. Range 5.00. Physical damage (3 hits × (weapon damage + Dexterity x60%)). Choose 3 targets in order; repeats allowed; confirm to fire. Affects: enemies. Ranged weapon required.</x:v>
+        <x:v>Magic ability. Cast. Range 0.00. Focus for 2 turns. +2 Strength, +2 Dexterity, +2 Intelligence. Positive status. Affects: self. No weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
@@ -567,7 +567,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R914301fd4b7b4699"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R061cfa2b1f084a94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -698,13 +698,13 @@
         <x:v>Cleric</x:v>
       </x:c>
       <x:c r="C9" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="23" t="str">
-        <x:v>Beam</x:v>
+        <x:v>Focus</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
-        <x:v>Magic ability. Cast. Range 3.00. Magical damage (10 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Line from caster toward target. No weapon required.</x:v>
+        <x:v>Magic ability. Cast. Range 0.00. Focus for 2 turns. +2 Strength, +2 Dexterity, +2 Intelligence. Positive status. Affects: self. No weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
@@ -718,10 +718,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>Focus</x:v>
+        <x:v>Beam</x:v>
       </x:c>
       <x:c r="E10" s="19" t="str">
-        <x:v>Magic ability. Cast. Range 0.00. Focus for 2 turns. +2 Strength, +2 Dexterity, +2 Intelligence. Positive status. Affects: self. No weapon required.</x:v>
+        <x:v>Magic ability. Cast. Range 5.00. Magical damage (10 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Line from caster toward target. No weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="57" customHeight="1">
@@ -764,7 +764,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f9643b0c6c4458e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffde7ddaff8e4e80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1012,7 +1012,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde17544857ef4880"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R683313d513504dba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1129,13 +1129,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
-        <x:v>Ice Shard</x:v>
+        <x:v>Fireball</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>Magic ability. Projectile. Range 5.00. Magical damage (15 innate + Intelligence x100%), Slow: Reduce Movement Range by 30% for 2 turns. Negative status. Affects: enemies. No weapon required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="57" customHeight="1">
+        <x:v>Magic ability. Projectile. Range 8.00. Magical damage (10 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Area: circle, 7-cell span. No weapon required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1146,13 +1146,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="23" t="str">
-        <x:v>Searing Dagger</x:v>
+        <x:v>Ice Shard</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
-        <x:v>Magic ability. Projectile. Range 8.00. Magical damage (15 innate + Intelligence x100%), Burning: 1 magical damage at turn start for 2 turns. Negative status. Affects: enemies. No weapon required.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+        <x:v>Magic ability. Projectile. Range 5.00. Magical damage (15 innate + Intelligence x100%), Slow: Reduce Movement Range by 30% for 2 turns. Negative status. Affects: enemies. No weapon required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="57" customHeight="1">
       <x:c r="A10" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1160,13 +1160,13 @@
         <x:v>Wizard</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>Slow</x:v>
+        <x:v>Searing Dagger</x:v>
       </x:c>
       <x:c r="E10" s="19" t="str">
-        <x:v>Magic ability. Cast. Range 5.00. Slow: Reduce Movement Range by 30% for 2 turns. Negative status. Affects: enemies. No weapon required.</x:v>
+        <x:v>Magic ability. Projectile. Range 8.00. Magical damage (15 innate + Intelligence x100%), Burning: 1 magical damage at turn start for 2 turns. Negative status. Affects: enemies. No weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -1177,13 +1177,13 @@
         <x:v>Wizard</x:v>
       </x:c>
       <x:c r="C11" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D11" s="23" t="str">
-        <x:v>Fireball</x:v>
+        <x:v>Slow</x:v>
       </x:c>
       <x:c r="E11" s="23" t="str">
-        <x:v>Magic ability. Projectile. Range 8.00. Magical damage (20 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Area: circle, 7-cell span. No weapon required.</x:v>
+        <x:v>Magic ability. Cast. Range 5.00. Slow: Reduce Movement Range by 30% for 2 turns. Negative status. Affects: enemies. No weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
@@ -1200,7 +1200,7 @@
         <x:v>Beam</x:v>
       </x:c>
       <x:c r="E12" s="19" t="str">
-        <x:v>Magic ability. Cast. Range 3.00. Magical damage (10 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Line from caster toward target. No weapon required.</x:v>
+        <x:v>Magic ability. Cast. Range 5.00. Magical damage (10 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Line from caster toward target. No weapon required.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1209,7 +1209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a06072b50794f73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807aeb955da64db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/CLASS_ABILITIES.xlsx
+++ b/CLASS_ABILITIES.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="R1ab8ac45c29b4288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R88a8eb222de94449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="Rc6e88f29e3464958"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="Rd58e949af40e4fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="R8ddaf0e317fa4e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R558d3e0230d84f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="R1b56a7eb5df943dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="R58e2d3f33e294eba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -567,7 +567,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R061cfa2b1f084a94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7709501438a9456b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -764,7 +764,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffde7ddaff8e4e80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0226d02a7fbf4d46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1012,7 +1012,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R683313d513504dba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R765c52455b044463"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1132,7 +1132,7 @@
         <x:v>Fireball</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>Magic ability. Projectile. Range 8.00. Magical damage (10 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Area: circle, 7-cell span. No weapon required.</x:v>
+        <x:v>Magic ability. Projectile. Range 8.00. Magical damage (5 innate + Intelligence x100%). Affects: enemies. Can aim at a cell. Area: circle, 5-cell span. No weapon required.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -1209,7 +1209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807aeb955da64db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4406395fd39742f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/CLASS_ABILITIES.xlsx
+++ b/CLASS_ABILITIES.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="R8ddaf0e317fa4e43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="R558d3e0230d84f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="R1b56a7eb5df943dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="R58e2d3f33e294eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archer" sheetId="1" r:id="Rb4293da37ca84832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleric" sheetId="2" r:id="Re793792cc9cf4331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warrior" sheetId="3" r:id="Rc48feacebee24156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wizard" sheetId="4" r:id="Ra6d0af1db35e4e79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,16 +71,30 @@
     </x:fill>
   </x:fills>
   <x:borders count="3">
-    <x:border/>
     <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
       <x:bottom style="thin">
         <x:color rgb="FFC7D0DB"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
     <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
       <x:bottom style="thin">
         <x:color rgb="FFDCE3EB"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
@@ -567,7 +581,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7709501438a9456b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34dcd92173494eb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -764,7 +778,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0226d02a7fbf4d46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reedbe56064c247ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1012,7 +1026,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R765c52455b044463"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7ebf0ad0b194742"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1209,7 +1223,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4406395fd39742f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2902bdddee50421e"/>
   </x:tableParts>
 </x:worksheet>
 </file>